--- a/R_Codes/DataSummary/Archaea/Sample_name/Archaea_Summary_Phylum_by_Sample_name.xlsx
+++ b/R_Codes/DataSummary/Archaea/Sample_name/Archaea_Summary_Phylum_by_Sample_name.xlsx
@@ -424,10 +424,10 @@
         <v>5</v>
       </c>
       <c r="C2" t="n">
-        <v>37.5981335300299</v>
+        <v>37.6146473286662</v>
       </c>
       <c r="D2" t="n">
-        <v>5.43780579940605</v>
+        <v>5.44204486329326</v>
       </c>
     </row>
     <row r="3">
@@ -438,10 +438,10 @@
         <v>6</v>
       </c>
       <c r="C3" t="n">
-        <v>27.8117884667471</v>
+        <v>27.8026265705646</v>
       </c>
       <c r="D3" t="n">
-        <v>2.20339118531641</v>
+        <v>2.20223176165201</v>
       </c>
     </row>
     <row r="4">
@@ -452,10 +452,10 @@
         <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>11.8220727936251</v>
+        <v>11.8162315611905</v>
       </c>
       <c r="D4" t="n">
-        <v>0.242385998194631</v>
+        <v>0.242172248980803</v>
       </c>
     </row>
     <row r="5">
@@ -466,10 +466,10 @@
         <v>8</v>
       </c>
       <c r="C5" t="n">
-        <v>8.88901069610624</v>
+        <v>8.88844499732014</v>
       </c>
       <c r="D5" t="n">
-        <v>1.03006933302267</v>
+        <v>1.029953565748</v>
       </c>
     </row>
     <row r="6">
@@ -480,10 +480,10 @@
         <v>9</v>
       </c>
       <c r="C6" t="n">
-        <v>4.26967222633716</v>
+        <v>4.26749999551657</v>
       </c>
       <c r="D6" t="n">
-        <v>0.136065425139798</v>
+        <v>0.136006692264525</v>
       </c>
     </row>
     <row r="7">
@@ -494,10 +494,10 @@
         <v>10</v>
       </c>
       <c r="C7" t="n">
-        <v>3.9729326695529</v>
+        <v>3.97238300902322</v>
       </c>
       <c r="D7" t="n">
-        <v>0.254739810951088</v>
+        <v>0.254653796306586</v>
       </c>
     </row>
     <row r="8">
@@ -508,10 +508,10 @@
         <v>11</v>
       </c>
       <c r="C8" t="n">
-        <v>1.88473328101322</v>
+        <v>1.88391134870761</v>
       </c>
       <c r="D8" t="n">
-        <v>0.343710074530966</v>
+        <v>0.343557938194633</v>
       </c>
     </row>
     <row r="9">
@@ -522,10 +522,10 @@
         <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>1.60491681905068</v>
+        <v>1.60475341957924</v>
       </c>
       <c r="D9" t="n">
-        <v>0.203347398935847</v>
+        <v>0.203320697582051</v>
       </c>
     </row>
     <row r="10">
@@ -536,10 +536,10 @@
         <v>13</v>
       </c>
       <c r="C10" t="n">
-        <v>1.37355874984232</v>
+        <v>1.37632070583837</v>
       </c>
       <c r="D10" t="n">
-        <v>0.608027825036764</v>
+        <v>0.609441380320974</v>
       </c>
     </row>
     <row r="11">
@@ -550,10 +550,10 @@
         <v>14</v>
       </c>
       <c r="C11" t="n">
-        <v>0.570696604569932</v>
+        <v>0.570543385000029</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0397467103015742</v>
+        <v>0.0397296146842208</v>
       </c>
     </row>
     <row r="12">
@@ -564,10 +564,10 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>0.10336839725838</v>
+        <v>0.10349339817975</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0254780013641728</v>
+        <v>0.0254968433941032</v>
       </c>
     </row>
     <row r="13">
@@ -578,10 +578,10 @@
         <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0991157658669333</v>
+        <v>0.0991442804136611</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0174851506219885</v>
+        <v>0.0174930856340913</v>
       </c>
     </row>
   </sheetData>
@@ -617,10 +617,10 @@
         <v>5</v>
       </c>
       <c r="C2" t="n">
-        <v>59.7972040101877</v>
+        <v>60.0117510250063</v>
       </c>
       <c r="D2" t="n">
-        <v>18.976589310687</v>
+        <v>19.0438950283452</v>
       </c>
     </row>
     <row r="3">
@@ -631,10 +631,10 @@
         <v>11</v>
       </c>
       <c r="C3" t="n">
-        <v>32.2028914218349</v>
+        <v>32.098927077113</v>
       </c>
       <c r="D3" t="n">
-        <v>0.323363422290218</v>
+        <v>0.3222473181677</v>
       </c>
     </row>
     <row r="4">
@@ -645,10 +645,10 @@
         <v>18</v>
       </c>
       <c r="C4" t="n">
-        <v>1.93891184712223</v>
+        <v>1.93261553258066</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0663761273090235</v>
+        <v>0.0661212506766528</v>
       </c>
     </row>
     <row r="5">
@@ -659,10 +659,10 @@
         <v>9</v>
       </c>
       <c r="C5" t="n">
-        <v>1.73075091445215</v>
+        <v>1.72381281041984</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0592720139891462</v>
+        <v>0.0588899026502082</v>
       </c>
     </row>
     <row r="6">
@@ -673,10 +673,10 @@
         <v>6</v>
       </c>
       <c r="C6" t="n">
-        <v>1.32965552382153</v>
+        <v>1.29822939103931</v>
       </c>
       <c r="D6" t="n">
-        <v>0.163439465682294</v>
+        <v>0.157336565818346</v>
       </c>
     </row>
     <row r="7">
@@ -687,10 +687,10 @@
         <v>8</v>
       </c>
       <c r="C7" t="n">
-        <v>1.32331005636933</v>
+        <v>1.26449200613915</v>
       </c>
       <c r="D7" t="n">
-        <v>0.310923335917212</v>
+        <v>0.293011298259827</v>
       </c>
     </row>
     <row r="8">
@@ -701,10 +701,10 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>0.954502856650244</v>
+        <v>0.951599115313579</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0704228505917791</v>
+        <v>0.0702002637596548</v>
       </c>
     </row>
     <row r="9">
@@ -715,10 +715,10 @@
         <v>10</v>
       </c>
       <c r="C9" t="n">
-        <v>0.471306513325133</v>
+        <v>0.470088527818709</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0164315430986118</v>
+        <v>0.0163901011625428</v>
       </c>
     </row>
     <row r="10">
@@ -729,10 +729,10 @@
         <v>12</v>
       </c>
       <c r="C10" t="n">
-        <v>0.132284452778502</v>
+        <v>0.13250593027904</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0278585800252594</v>
+        <v>0.0279680233633284</v>
       </c>
     </row>
     <row r="11">
@@ -743,10 +743,10 @@
         <v>14</v>
       </c>
       <c r="C11" t="n">
-        <v>0.108520301484974</v>
+        <v>0.105343591806292</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0146072490474575</v>
+        <v>0.0136460636697803</v>
       </c>
     </row>
     <row r="12">
@@ -757,7 +757,7 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>0.00613877383033067</v>
+        <v>0.00612320169641204</v>
       </c>
       <c r="D12"/>
     </row>
@@ -769,7 +769,7 @@
         <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>0.00452332814272972</v>
+        <v>0.00451179078774197</v>
       </c>
       <c r="D13"/>
     </row>
@@ -806,10 +806,10 @@
         <v>6</v>
       </c>
       <c r="C2" t="n">
-        <v>18.6367855516225</v>
+        <v>18.6381271274119</v>
       </c>
       <c r="D2" t="n">
-        <v>1.01391049972148</v>
+        <v>1.01399917766499</v>
       </c>
     </row>
     <row r="3">
@@ -820,10 +820,10 @@
         <v>9</v>
       </c>
       <c r="C3" t="n">
-        <v>18.5202533685736</v>
+        <v>18.5201013097571</v>
       </c>
       <c r="D3" t="n">
-        <v>0.505976770488784</v>
+        <v>0.505976909932865</v>
       </c>
     </row>
     <row r="4">
@@ -834,10 +834,10 @@
         <v>5</v>
       </c>
       <c r="C4" t="n">
-        <v>16.8253760374375</v>
+        <v>16.821080099086</v>
       </c>
       <c r="D4" t="n">
-        <v>2.8292262726294</v>
+        <v>2.82827026926379</v>
       </c>
     </row>
     <row r="5">
@@ -848,10 +848,10 @@
         <v>10</v>
       </c>
       <c r="C5" t="n">
-        <v>12.7949943573805</v>
+        <v>12.7953779007157</v>
       </c>
       <c r="D5" t="n">
-        <v>0.416981391722336</v>
+        <v>0.41699354510049</v>
       </c>
     </row>
     <row r="6">
@@ -862,10 +862,10 @@
         <v>12</v>
       </c>
       <c r="C6" t="n">
-        <v>11.7452341318612</v>
+        <v>11.7458348323098</v>
       </c>
       <c r="D6" t="n">
-        <v>1.37682566368649</v>
+        <v>1.37689345146925</v>
       </c>
     </row>
     <row r="7">
@@ -876,10 +876,10 @@
         <v>7</v>
       </c>
       <c r="C7" t="n">
-        <v>6.95538214449839</v>
+        <v>6.95653878385309</v>
       </c>
       <c r="D7" t="n">
-        <v>0.051641360466749</v>
+        <v>0.0516579124591188</v>
       </c>
     </row>
     <row r="8">
@@ -890,10 +890,10 @@
         <v>8</v>
       </c>
       <c r="C8" t="n">
-        <v>6.11588517287203</v>
+        <v>6.1164324484389</v>
       </c>
       <c r="D8" t="n">
-        <v>0.616074763446808</v>
+        <v>0.616147299562352</v>
       </c>
     </row>
     <row r="9">
@@ -904,10 +904,10 @@
         <v>14</v>
       </c>
       <c r="C9" t="n">
-        <v>3.26312227248418</v>
+        <v>3.26300971531625</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0961006824323567</v>
+        <v>0.0960943283127623</v>
       </c>
     </row>
     <row r="10">
@@ -918,10 +918,10 @@
         <v>11</v>
       </c>
       <c r="C10" t="n">
-        <v>2.5737828917859</v>
+        <v>2.57427956123471</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0722211548597914</v>
+        <v>0.0722298071945715</v>
       </c>
     </row>
     <row r="11">
@@ -932,10 +932,10 @@
         <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>1.46754394593324</v>
+        <v>1.46756821441988</v>
       </c>
       <c r="D11" t="n">
-        <v>0.221908676469357</v>
+        <v>0.221914596352504</v>
       </c>
     </row>
     <row r="12">
@@ -946,10 +946,10 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>0.939262261327925</v>
+        <v>0.939235706664847</v>
       </c>
       <c r="D12" t="n">
-        <v>0.076588972054449</v>
+        <v>0.0765853287362225</v>
       </c>
     </row>
     <row r="13">
@@ -960,10 +960,10 @@
         <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>0.139326797297523</v>
+        <v>0.139357882061933</v>
       </c>
       <c r="D13" t="n">
-        <v>0.00657364646947169</v>
+        <v>0.00657574523047377</v>
       </c>
     </row>
     <row r="14">
@@ -974,7 +974,7 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0230510669255519</v>
+        <v>0.0230564187299055</v>
       </c>
       <c r="D14"/>
     </row>
